--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/UTAH_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/UTAH_2019.xlsx
@@ -1705,7 +1705,7 @@
         <v>8</v>
       </c>
       <c r="D75">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="76">
@@ -1813,7 +1813,7 @@
         <v>8</v>
       </c>
       <c r="D81">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="82">
@@ -2137,7 +2137,7 @@
         <v>8</v>
       </c>
       <c r="D99">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="100">
@@ -3091,7 +3091,7 @@
         <v>8</v>
       </c>
       <c r="D152">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="153">
@@ -3829,7 +3829,7 @@
         <v>8</v>
       </c>
       <c r="D193">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="194">
@@ -4081,7 +4081,7 @@
         <v>8</v>
       </c>
       <c r="D207">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="208">
@@ -4621,7 +4621,7 @@
         <v>8</v>
       </c>
       <c r="D237">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="238">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C248">
@@ -4999,7 +4999,7 @@
         <v>81</v>
       </c>
       <c r="D258">
-        <v>0.009447165850244927</v>
+        <v>0.009447165850244929</v>
       </c>
     </row>
     <row r="259">
@@ -5701,7 +5701,7 @@
         <v>8</v>
       </c>
       <c r="D297">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="298">
@@ -6115,7 +6115,7 @@
         <v>8</v>
       </c>
       <c r="D320">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="321">
@@ -6133,7 +6133,7 @@
         <v>8</v>
       </c>
       <c r="D321">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="322">
@@ -6835,7 +6835,7 @@
         <v>8</v>
       </c>
       <c r="D360">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="361">
@@ -8365,7 +8365,7 @@
         <v>8</v>
       </c>
       <c r="D445">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="446">
@@ -8653,7 +8653,7 @@
         <v>8</v>
       </c>
       <c r="D461">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="462">
@@ -9139,7 +9139,7 @@
         <v>8</v>
       </c>
       <c r="D488">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="489">
@@ -9229,7 +9229,7 @@
         <v>8</v>
       </c>
       <c r="D493">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="494">
@@ -9499,7 +9499,7 @@
         <v>8</v>
       </c>
       <c r="D508">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="509">
@@ -9913,7 +9913,7 @@
         <v>8</v>
       </c>
       <c r="D531">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="532">
@@ -11245,7 +11245,7 @@
         <v>8</v>
       </c>
       <c r="D605">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="606">
@@ -11371,7 +11371,7 @@
         <v>8</v>
       </c>
       <c r="D612">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="613">
@@ -11515,7 +11515,7 @@
         <v>8</v>
       </c>
       <c r="D620">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="621">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C691">
@@ -13603,7 +13603,7 @@
         <v>8</v>
       </c>
       <c r="D736">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="737">
@@ -13729,7 +13729,7 @@
         <v>8</v>
       </c>
       <c r="D743">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="744">
@@ -13909,7 +13909,7 @@
         <v>8</v>
       </c>
       <c r="D753">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="754">
@@ -15817,7 +15817,7 @@
         <v>8</v>
       </c>
       <c r="D859">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="860">
@@ -16735,7 +16735,7 @@
         <v>8</v>
       </c>
       <c r="D910">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="911">
@@ -17545,7 +17545,7 @@
         <v>8</v>
       </c>
       <c r="D955">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="956">
@@ -18517,7 +18517,7 @@
         <v>8</v>
       </c>
       <c r="D1009">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="1010">
@@ -19399,7 +19399,7 @@
         <v>8</v>
       </c>
       <c r="D1058">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="1059">
@@ -19471,7 +19471,7 @@
         <v>8</v>
       </c>
       <c r="D1062">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="1063">
@@ -20443,7 +20443,7 @@
         <v>8</v>
       </c>
       <c r="D1116">
-        <v>0.0009330534173081409</v>
+        <v>0.0009330534173081408</v>
       </c>
     </row>
     <row r="1117">
